--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122246733</v>
+        <v>122246765</v>
       </c>
       <c r="B2" t="n">
-        <v>57527</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321530</v>
+        <v>321732</v>
       </c>
       <c r="R2" t="n">
-        <v>6430805</v>
+        <v>6430948</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,24 +756,14 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I talldominerad, skiktad skog nära mossen.</t>
+          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122246664</v>
+        <v>122246733</v>
       </c>
       <c r="B3" t="n">
-        <v>57744</v>
+        <v>57527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,30 +802,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -852,17 +838,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1291-2025, Boh</t>
+          <t>Dyfjällernas mosse, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321869</v>
+        <v>321530</v>
       </c>
       <c r="R3" t="n">
-        <v>6430770</v>
+        <v>6430805</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -901,12 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 2 ex.</t>
+          <t>I talldominerad, skiktad skog nära mossen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122246765</v>
+        <v>122246664</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>57744</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,20 +931,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -966,28 +952,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, väster om, Boh</t>
+          <t>A 1291-2025, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321732</v>
+        <v>321869</v>
       </c>
       <c r="R4" t="n">
-        <v>6430948</v>
+        <v>6430770</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,14 +1004,24 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122283992</v>
+        <v>122283857</v>
       </c>
       <c r="B5" t="n">
-        <v>97129</v>
+        <v>97121</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,38 +1064,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321665</v>
+        <v>321728</v>
       </c>
       <c r="R5" t="n">
-        <v>6430914</v>
+        <v>6430954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,7 +1172,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122284062</v>
+        <v>122283992</v>
       </c>
       <c r="B6" t="n">
         <v>97129</v>
@@ -1200,14 +1212,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321729</v>
+        <v>321665</v>
       </c>
       <c r="R6" t="n">
-        <v>6430964</v>
+        <v>6430914</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1256,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1396,10 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122283846</v>
+        <v>122284062</v>
       </c>
       <c r="B8" t="n">
-        <v>97121</v>
+        <v>97129</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,50 +1424,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321686</v>
+        <v>321729</v>
       </c>
       <c r="R8" t="n">
-        <v>6430924</v>
+        <v>6430964</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Följeväxt äkta lopplummer.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,7 +1520,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122283857</v>
+        <v>122283846</v>
       </c>
       <c r="B9" t="n">
         <v>97121</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1572,14 +1572,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321728</v>
+        <v>321686</v>
       </c>
       <c r="R9" t="n">
-        <v>6430954</v>
+        <v>6430924</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122246765</v>
+        <v>122246733</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, väster om, Boh</t>
+          <t>Dyfjällernas mosse, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321732</v>
+        <v>321530</v>
       </c>
       <c r="R2" t="n">
-        <v>6430948</v>
+        <v>6430805</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,14 +760,24 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
+          <t>I talldominerad, skiktad skog nära mossen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122246733</v>
+        <v>122246765</v>
       </c>
       <c r="B3" t="n">
-        <v>57527</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,46 +820,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321530</v>
+        <v>321732</v>
       </c>
       <c r="R3" t="n">
-        <v>6430805</v>
+        <v>6430948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,24 +885,14 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I talldominerad, skiktad skog nära mossen.</t>
+          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122283857</v>
+        <v>122284108</v>
       </c>
       <c r="B5" t="n">
-        <v>97121</v>
+        <v>97131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1100,14 +1100,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321728</v>
+        <v>321607</v>
       </c>
       <c r="R5" t="n">
-        <v>6430954</v>
+        <v>6430823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+          <t>Nordvänd hällmark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122283992</v>
+        <v>122283857</v>
       </c>
       <c r="B6" t="n">
-        <v>97129</v>
+        <v>97131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,38 +1188,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321665</v>
+        <v>321728</v>
       </c>
       <c r="R6" t="n">
-        <v>6430914</v>
+        <v>6430954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1268,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122284108</v>
+        <v>122283846</v>
       </c>
       <c r="B7" t="n">
-        <v>97121</v>
+        <v>97131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1319,7 +1331,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1336,14 +1348,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321607</v>
+        <v>321686</v>
       </c>
       <c r="R7" t="n">
-        <v>6430823</v>
+        <v>6430924</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,7 +1392,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark.</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,10 +1420,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122284062</v>
+        <v>122283992</v>
       </c>
       <c r="B8" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1448,14 +1460,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321729</v>
+        <v>321665</v>
       </c>
       <c r="R8" t="n">
-        <v>6430964</v>
+        <v>6430914</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1504,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,10 +1532,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122283846</v>
+        <v>122284062</v>
       </c>
       <c r="B9" t="n">
-        <v>97121</v>
+        <v>97139</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1536,50 +1548,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321686</v>
+        <v>321729</v>
       </c>
       <c r="R9" t="n">
-        <v>6430924</v>
+        <v>6430964</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Följeväxt äkta lopplummer.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122246733</v>
+        <v>122246765</v>
       </c>
       <c r="B2" t="n">
-        <v>57527</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321530</v>
+        <v>321732</v>
       </c>
       <c r="R2" t="n">
-        <v>6430805</v>
+        <v>6430948</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,24 +756,14 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I talldominerad, skiktad skog nära mossen.</t>
+          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122246765</v>
+        <v>122246733</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,42 +806,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, väster om, Boh</t>
+          <t>Dyfjällernas mosse, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321732</v>
+        <v>321530</v>
       </c>
       <c r="R3" t="n">
-        <v>6430948</v>
+        <v>6430805</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,14 +875,24 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
+          <t>I talldominerad, skiktad skog nära mossen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1048,7 +1048,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122284108</v>
+        <v>122283857</v>
       </c>
       <c r="B5" t="n">
         <v>97131</v>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1100,14 +1100,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321607</v>
+        <v>321728</v>
       </c>
       <c r="R5" t="n">
-        <v>6430823</v>
+        <v>6430954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark.</t>
+          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,7 +1172,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122283857</v>
+        <v>122284108</v>
       </c>
       <c r="B6" t="n">
         <v>97131</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1224,14 +1224,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321728</v>
+        <v>321607</v>
       </c>
       <c r="R6" t="n">
-        <v>6430954</v>
+        <v>6430823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+          <t>Nordvänd hällmark.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122283846</v>
+        <v>122283992</v>
       </c>
       <c r="B7" t="n">
-        <v>97131</v>
+        <v>97139</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,50 +1312,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321686</v>
+        <v>321665</v>
       </c>
       <c r="R7" t="n">
-        <v>6430924</v>
+        <v>6430914</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1392,7 +1380,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,10 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122283992</v>
+        <v>122283846</v>
       </c>
       <c r="B8" t="n">
-        <v>97139</v>
+        <v>97131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,38 +1424,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321665</v>
+        <v>321686</v>
       </c>
       <c r="R8" t="n">
-        <v>6430914</v>
+        <v>6430924</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122246765</v>
+        <v>122246733</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, väster om, Boh</t>
+          <t>Dyfjällernas mosse, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321732</v>
+        <v>321530</v>
       </c>
       <c r="R2" t="n">
-        <v>6430948</v>
+        <v>6430805</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,14 +760,24 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
+          <t>I talldominerad, skiktad skog nära mossen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122246733</v>
+        <v>122246664</v>
       </c>
       <c r="B3" t="n">
-        <v>57527</v>
+        <v>57749</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,30 +816,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -838,17 +852,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, Boh</t>
+          <t>A 1291-2025, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321530</v>
+        <v>321869</v>
       </c>
       <c r="R3" t="n">
-        <v>6430805</v>
+        <v>6430770</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +901,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I talldominerad, skiktad skog nära mossen.</t>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122246664</v>
+        <v>122246765</v>
       </c>
       <c r="B4" t="n">
-        <v>57744</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,20 +945,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -952,32 +966,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 1291-2025, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321869</v>
+        <v>321732</v>
       </c>
       <c r="R4" t="n">
-        <v>6430770</v>
+        <v>6430948</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,24 +1014,14 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 2 ex.</t>
+          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122283857</v>
+        <v>122284108</v>
       </c>
       <c r="B5" t="n">
-        <v>97131</v>
+        <v>97143</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1100,14 +1100,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321728</v>
+        <v>321607</v>
       </c>
       <c r="R5" t="n">
-        <v>6430954</v>
+        <v>6430823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+          <t>Nordvänd hällmark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122284108</v>
+        <v>122284062</v>
       </c>
       <c r="B6" t="n">
-        <v>97131</v>
+        <v>97151</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,50 +1188,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321607</v>
+        <v>321729</v>
       </c>
       <c r="R6" t="n">
-        <v>6430823</v>
+        <v>6430964</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,7 +1256,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark.</t>
+          <t>Följeväxt äkta lopplummer.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122283992</v>
+        <v>122283846</v>
       </c>
       <c r="B7" t="n">
-        <v>97139</v>
+        <v>97143</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,38 +1300,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321665</v>
+        <v>321686</v>
       </c>
       <c r="R7" t="n">
-        <v>6430914</v>
+        <v>6430924</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,10 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122283846</v>
+        <v>122283992</v>
       </c>
       <c r="B8" t="n">
-        <v>97131</v>
+        <v>97151</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1424,50 +1424,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321686</v>
+        <v>321665</v>
       </c>
       <c r="R8" t="n">
-        <v>6430924</v>
+        <v>6430914</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1492,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122284062</v>
+        <v>122283857</v>
       </c>
       <c r="B9" t="n">
-        <v>97139</v>
+        <v>97143</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,38 +1536,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321729</v>
+        <v>321728</v>
       </c>
       <c r="R9" t="n">
-        <v>6430964</v>
+        <v>6430954</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer.</t>
+          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122246664</v>
+        <v>122246765</v>
       </c>
       <c r="B3" t="n">
-        <v>57749</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,20 +816,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,32 +837,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1291-2025, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321869</v>
+        <v>321732</v>
       </c>
       <c r="R3" t="n">
-        <v>6430770</v>
+        <v>6430948</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,24 +885,14 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 2 ex.</t>
+          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122246765</v>
+        <v>122246664</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>57749</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,20 +931,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -966,28 +952,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, väster om, Boh</t>
+          <t>A 1291-2025, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321732</v>
+        <v>321869</v>
       </c>
       <c r="R4" t="n">
-        <v>6430948</v>
+        <v>6430770</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,14 +1004,24 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122284108</v>
+        <v>122283992</v>
       </c>
       <c r="B5" t="n">
-        <v>97143</v>
+        <v>97156</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,38 +1064,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1104,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321607</v>
+        <v>321665</v>
       </c>
       <c r="R5" t="n">
-        <v>6430823</v>
+        <v>6430914</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1132,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122284062</v>
+        <v>122284108</v>
       </c>
       <c r="B6" t="n">
-        <v>97151</v>
+        <v>97148</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,38 +1176,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321729</v>
+        <v>321607</v>
       </c>
       <c r="R6" t="n">
-        <v>6430964</v>
+        <v>6430823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer.</t>
+          <t>Nordvänd hällmark.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122283846</v>
+        <v>122284062</v>
       </c>
       <c r="B7" t="n">
-        <v>97143</v>
+        <v>97156</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,50 +1300,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321686</v>
+        <v>321729</v>
       </c>
       <c r="R7" t="n">
-        <v>6430924</v>
+        <v>6430964</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,7 +1368,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Följeväxt äkta lopplummer.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122283992</v>
+        <v>122283857</v>
       </c>
       <c r="B8" t="n">
-        <v>97151</v>
+        <v>97148</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1424,38 +1412,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321665</v>
+        <v>321728</v>
       </c>
       <c r="R8" t="n">
-        <v>6430914</v>
+        <v>6430954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122283857</v>
+        <v>122283846</v>
       </c>
       <c r="B9" t="n">
-        <v>97143</v>
+        <v>97148</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1572,14 +1572,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321728</v>
+        <v>321686</v>
       </c>
       <c r="R9" t="n">
-        <v>6430954</v>
+        <v>6430924</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>103021</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -804,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122246765</v>
+        <v>122246664</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>57749</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,20 +811,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,28 +827,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, väster om, Boh</t>
+          <t>A 1291-2025, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321732</v>
+        <v>321869</v>
       </c>
       <c r="R3" t="n">
-        <v>6430948</v>
+        <v>6430770</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,14 +879,24 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122246664</v>
+        <v>122246765</v>
       </c>
       <c r="B4" t="n">
-        <v>57749</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,20 +935,15 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -952,32 +951,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 1291-2025, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321869</v>
+        <v>321732</v>
       </c>
       <c r="R4" t="n">
-        <v>6430770</v>
+        <v>6430948</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,24 +999,14 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 2 ex.</t>
+          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122283992</v>
+        <v>122284108</v>
       </c>
       <c r="B5" t="n">
-        <v>97156</v>
+        <v>97157</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,26 +1049,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>224361</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1092,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321665</v>
+        <v>321607</v>
       </c>
       <c r="R5" t="n">
-        <v>6430914</v>
+        <v>6430823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1124,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Nordvänd hällmark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122284108</v>
+        <v>122283992</v>
       </c>
       <c r="B6" t="n">
-        <v>97148</v>
+        <v>97165</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,38 +1168,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224361</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Äkta lopplummer</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1216,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321607</v>
+        <v>321665</v>
       </c>
       <c r="R6" t="n">
-        <v>6430823</v>
+        <v>6430914</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1231,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122284062</v>
+        <v>122283857</v>
       </c>
       <c r="B7" t="n">
-        <v>97156</v>
+        <v>97157</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,38 +1275,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>224361</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321729</v>
+        <v>321728</v>
       </c>
       <c r="R7" t="n">
-        <v>6430964</v>
+        <v>6430954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1350,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer.</t>
+          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122283857</v>
+        <v>122283846</v>
       </c>
       <c r="B8" t="n">
-        <v>97148</v>
+        <v>97157</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,11 +1396,6 @@
       <c r="E8" t="n">
         <v>224361</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Äkta lopplummer</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Huperzia europaea</t>
@@ -1431,7 +1408,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1448,14 +1425,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321728</v>
+        <v>321686</v>
       </c>
       <c r="R8" t="n">
-        <v>6430954</v>
+        <v>6430924</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1469,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122283846</v>
+        <v>122284062</v>
       </c>
       <c r="B9" t="n">
-        <v>97148</v>
+        <v>97165</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1536,50 +1513,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224361</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Äkta lopplummer</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321686</v>
+        <v>321729</v>
       </c>
       <c r="R9" t="n">
-        <v>6430924</v>
+        <v>6430964</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,7 +1576,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Följeväxt äkta lopplummer.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122246733</v>
+        <v>122246664</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>57753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -718,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, Boh</t>
+          <t>A 1291-2025, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321530</v>
+        <v>321869</v>
       </c>
       <c r="R2" t="n">
-        <v>6430805</v>
+        <v>6430770</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I talldominerad, skiktad skog nära mossen.</t>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122246664</v>
+        <v>122246765</v>
       </c>
       <c r="B3" t="n">
-        <v>57749</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,15 +816,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -827,32 +837,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1291-2025, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321869</v>
+        <v>321732</v>
       </c>
       <c r="R3" t="n">
-        <v>6430770</v>
+        <v>6430948</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,24 +885,14 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 2 ex.</t>
+          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122246765</v>
+        <v>122246733</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,37 +935,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, väster om, Boh</t>
+          <t>Dyfjällernas mosse, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321732</v>
+        <v>321530</v>
       </c>
       <c r="R4" t="n">
-        <v>6430948</v>
+        <v>6430805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,14 +1004,24 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
+          <t>I talldominerad, skiktad skog nära mossen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +1051,7 @@
         <v>122284108</v>
       </c>
       <c r="B5" t="n">
-        <v>97157</v>
+        <v>97170</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,6 +1065,11 @@
       </c>
       <c r="E5" t="n">
         <v>224361</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1152,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122283992</v>
+        <v>122283846</v>
       </c>
       <c r="B6" t="n">
-        <v>97165</v>
+        <v>97170</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,33 +1188,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>224361</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321665</v>
+        <v>321686</v>
       </c>
       <c r="R6" t="n">
-        <v>6430914</v>
+        <v>6430924</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1268,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122283857</v>
+        <v>122284062</v>
       </c>
       <c r="B7" t="n">
-        <v>97157</v>
+        <v>97178</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,45 +1312,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224361</v>
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321728</v>
+        <v>321729</v>
       </c>
       <c r="R7" t="n">
-        <v>6430954</v>
+        <v>6430964</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1380,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+          <t>Följeväxt äkta lopplummer.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,10 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122283846</v>
+        <v>122283857</v>
       </c>
       <c r="B8" t="n">
-        <v>97157</v>
+        <v>97170</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,6 +1426,11 @@
       <c r="E8" t="n">
         <v>224361</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Huperzia europaea</t>
@@ -1408,7 +1443,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1425,14 +1460,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321686</v>
+        <v>321728</v>
       </c>
       <c r="R8" t="n">
-        <v>6430924</v>
+        <v>6430954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1504,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1532,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122284062</v>
+        <v>122283992</v>
       </c>
       <c r="B9" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,6 +1549,11 @@
       </c>
       <c r="E9" t="n">
         <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1532,14 +1572,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321729</v>
+        <v>321665</v>
       </c>
       <c r="R9" t="n">
-        <v>6430964</v>
+        <v>6430914</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,7 +1616,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122246664</v>
+        <v>122246765</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,32 +708,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 1291-2025, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321869</v>
+        <v>321732</v>
       </c>
       <c r="R2" t="n">
-        <v>6430770</v>
+        <v>6430948</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,24 +756,14 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 2 ex.</t>
+          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122246765</v>
+        <v>122246733</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,42 +806,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, väster om, Boh</t>
+          <t>Dyfjällernas mosse, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321732</v>
+        <v>321530</v>
       </c>
       <c r="R3" t="n">
-        <v>6430948</v>
+        <v>6430805</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,14 +875,24 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
+          <t>I talldominerad, skiktad skog nära mossen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122246733</v>
+        <v>122246664</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,30 +931,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -967,17 +967,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, Boh</t>
+          <t>A 1291-2025, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321530</v>
+        <v>321869</v>
       </c>
       <c r="R4" t="n">
-        <v>6430805</v>
+        <v>6430770</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I talldominerad, skiktad skog nära mossen.</t>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,7 +1051,7 @@
         <v>122284108</v>
       </c>
       <c r="B5" t="n">
-        <v>97170</v>
+        <v>97183</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122283846</v>
+        <v>122283992</v>
       </c>
       <c r="B6" t="n">
-        <v>97170</v>
+        <v>97191</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,50 +1188,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321686</v>
+        <v>321665</v>
       </c>
       <c r="R6" t="n">
-        <v>6430924</v>
+        <v>6430914</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,7 +1256,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,7 +1287,7 @@
         <v>122284062</v>
       </c>
       <c r="B7" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1408,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122283857</v>
+        <v>122283846</v>
       </c>
       <c r="B8" t="n">
-        <v>97170</v>
+        <v>97183</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,7 +1431,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1460,14 +1448,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321728</v>
+        <v>321686</v>
       </c>
       <c r="R8" t="n">
-        <v>6430954</v>
+        <v>6430924</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1492,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122283992</v>
+        <v>122283857</v>
       </c>
       <c r="B9" t="n">
-        <v>97178</v>
+        <v>97183</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,38 +1536,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321665</v>
+        <v>321728</v>
       </c>
       <c r="R9" t="n">
-        <v>6430914</v>
+        <v>6430954</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -1172,7 +1172,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122283992</v>
+        <v>122284062</v>
       </c>
       <c r="B6" t="n">
         <v>97191</v>
@@ -1212,14 +1212,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321665</v>
+        <v>321729</v>
       </c>
       <c r="R6" t="n">
-        <v>6430914</v>
+        <v>6430964</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Följeväxt äkta lopplummer.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122284062</v>
+        <v>122283857</v>
       </c>
       <c r="B7" t="n">
-        <v>97191</v>
+        <v>97183</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,38 +1300,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321729</v>
+        <v>321728</v>
       </c>
       <c r="R7" t="n">
-        <v>6430964</v>
+        <v>6430954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1380,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer.</t>
+          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122283846</v>
+        <v>122283992</v>
       </c>
       <c r="B8" t="n">
-        <v>97183</v>
+        <v>97191</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,50 +1424,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321686</v>
+        <v>321665</v>
       </c>
       <c r="R8" t="n">
-        <v>6430924</v>
+        <v>6430914</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,7 +1520,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122283857</v>
+        <v>122283846</v>
       </c>
       <c r="B9" t="n">
         <v>97183</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1572,14 +1572,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321728</v>
+        <v>321686</v>
       </c>
       <c r="R9" t="n">
-        <v>6430954</v>
+        <v>6430924</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122284108</v>
+        <v>122284062</v>
       </c>
       <c r="B5" t="n">
-        <v>97183</v>
+        <v>97191</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,50 +1064,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321607</v>
+        <v>321729</v>
       </c>
       <c r="R5" t="n">
-        <v>6430823</v>
+        <v>6430964</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1132,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark.</t>
+          <t>Följeväxt äkta lopplummer.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122284062</v>
+        <v>122284108</v>
       </c>
       <c r="B6" t="n">
-        <v>97191</v>
+        <v>97183</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,38 +1176,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321729</v>
+        <v>321607</v>
       </c>
       <c r="R6" t="n">
-        <v>6430964</v>
+        <v>6430823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer.</t>
+          <t>Nordvänd hällmark.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122246765</v>
+        <v>122246733</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, väster om, Boh</t>
+          <t>Dyfjällernas mosse, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321732</v>
+        <v>321530</v>
       </c>
       <c r="R2" t="n">
-        <v>6430948</v>
+        <v>6430805</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,14 +760,24 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
+          <t>I talldominerad, skiktad skog nära mossen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122246733</v>
+        <v>122246664</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,30 +816,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -838,17 +852,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, Boh</t>
+          <t>A 1291-2025, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321530</v>
+        <v>321869</v>
       </c>
       <c r="R3" t="n">
-        <v>6430805</v>
+        <v>6430770</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +901,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I talldominerad, skiktad skog nära mossen.</t>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122246664</v>
+        <v>122246765</v>
       </c>
       <c r="B4" t="n">
-        <v>57753</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,20 +945,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -952,32 +966,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 1291-2025, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321869</v>
+        <v>321732</v>
       </c>
       <c r="R4" t="n">
-        <v>6430770</v>
+        <v>6430948</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,24 +1014,14 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 2 ex.</t>
+          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,7 +1051,7 @@
         <v>122284062</v>
       </c>
       <c r="B5" t="n">
-        <v>97191</v>
+        <v>97194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122284108</v>
+        <v>122283992</v>
       </c>
       <c r="B6" t="n">
-        <v>97183</v>
+        <v>97194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,38 +1176,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1216,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321607</v>
+        <v>321665</v>
       </c>
       <c r="R6" t="n">
-        <v>6430823</v>
+        <v>6430914</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122283857</v>
+        <v>122283846</v>
       </c>
       <c r="B7" t="n">
-        <v>97183</v>
+        <v>97186</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1319,7 +1307,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1336,14 +1324,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321728</v>
+        <v>321686</v>
       </c>
       <c r="R7" t="n">
-        <v>6430954</v>
+        <v>6430924</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,7 +1368,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122283992</v>
+        <v>122284108</v>
       </c>
       <c r="B8" t="n">
-        <v>97191</v>
+        <v>97186</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1424,26 +1412,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321665</v>
+        <v>321607</v>
       </c>
       <c r="R8" t="n">
-        <v>6430914</v>
+        <v>6430823</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Nordvänd hällmark.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122283846</v>
+        <v>122283857</v>
       </c>
       <c r="B9" t="n">
-        <v>97183</v>
+        <v>97186</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1572,14 +1572,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321686</v>
+        <v>321728</v>
       </c>
       <c r="R9" t="n">
-        <v>6430924</v>
+        <v>6430954</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122246664</v>
+        <v>122246765</v>
       </c>
       <c r="B3" t="n">
-        <v>57753</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,20 +816,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,32 +837,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1291-2025, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321869</v>
+        <v>321732</v>
       </c>
       <c r="R3" t="n">
-        <v>6430770</v>
+        <v>6430948</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,24 +885,14 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 2 ex.</t>
+          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122246765</v>
+        <v>122246664</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,20 +931,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -966,28 +952,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, väster om, Boh</t>
+          <t>A 1291-2025, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321732</v>
+        <v>321869</v>
       </c>
       <c r="R4" t="n">
-        <v>6430948</v>
+        <v>6430770</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,14 +1004,24 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122284062</v>
+        <v>122284108</v>
       </c>
       <c r="B5" t="n">
-        <v>97194</v>
+        <v>97186</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,38 +1064,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321729</v>
+        <v>321607</v>
       </c>
       <c r="R5" t="n">
-        <v>6430964</v>
+        <v>6430823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer.</t>
+          <t>Nordvänd hällmark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122283992</v>
+        <v>122283846</v>
       </c>
       <c r="B6" t="n">
-        <v>97194</v>
+        <v>97186</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,38 +1188,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321665</v>
+        <v>321686</v>
       </c>
       <c r="R6" t="n">
-        <v>6430914</v>
+        <v>6430924</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1268,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122283846</v>
+        <v>122283992</v>
       </c>
       <c r="B7" t="n">
-        <v>97186</v>
+        <v>97194</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,50 +1312,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321686</v>
+        <v>321665</v>
       </c>
       <c r="R7" t="n">
-        <v>6430924</v>
+        <v>6430914</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1380,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122284108</v>
+        <v>122284062</v>
       </c>
       <c r="B8" t="n">
-        <v>97186</v>
+        <v>97194</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,50 +1424,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321607</v>
+        <v>321729</v>
       </c>
       <c r="R8" t="n">
-        <v>6430823</v>
+        <v>6430964</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark.</t>
+          <t>Följeväxt äkta lopplummer.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122284108</v>
+        <v>122283846</v>
       </c>
       <c r="B5" t="n">
-        <v>97186</v>
+        <v>97187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1100,14 +1100,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321607</v>
+        <v>321686</v>
       </c>
       <c r="R5" t="n">
-        <v>6430823</v>
+        <v>6430924</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark.</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122283846</v>
+        <v>122283857</v>
       </c>
       <c r="B6" t="n">
-        <v>97186</v>
+        <v>97187</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1224,14 +1224,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321686</v>
+        <v>321728</v>
       </c>
       <c r="R6" t="n">
-        <v>6430924</v>
+        <v>6430954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122283992</v>
+        <v>122284108</v>
       </c>
       <c r="B7" t="n">
-        <v>97194</v>
+        <v>97187</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,26 +1312,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1340,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321665</v>
+        <v>321607</v>
       </c>
       <c r="R7" t="n">
-        <v>6430914</v>
+        <v>6430823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,7 +1392,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Nordvänd hällmark.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,7 +1423,7 @@
         <v>122284062</v>
       </c>
       <c r="B8" t="n">
-        <v>97194</v>
+        <v>97195</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1520,10 +1532,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122283857</v>
+        <v>122283992</v>
       </c>
       <c r="B9" t="n">
-        <v>97186</v>
+        <v>97195</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1536,50 +1548,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321728</v>
+        <v>321665</v>
       </c>
       <c r="R9" t="n">
-        <v>6430954</v>
+        <v>6430914</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122283846</v>
+        <v>122283992</v>
       </c>
       <c r="B5" t="n">
-        <v>97187</v>
+        <v>97198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,50 +1064,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321686</v>
+        <v>321665</v>
       </c>
       <c r="R5" t="n">
-        <v>6430924</v>
+        <v>6430914</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1132,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122283857</v>
+        <v>122283846</v>
       </c>
       <c r="B6" t="n">
-        <v>97187</v>
+        <v>97190</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,7 +1195,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1224,14 +1212,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321728</v>
+        <v>321686</v>
       </c>
       <c r="R6" t="n">
-        <v>6430954</v>
+        <v>6430924</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,7 +1256,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,7 +1287,7 @@
         <v>122284108</v>
       </c>
       <c r="B7" t="n">
-        <v>97187</v>
+        <v>97190</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1423,7 +1411,7 @@
         <v>122284062</v>
       </c>
       <c r="B8" t="n">
-        <v>97195</v>
+        <v>97198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1532,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122283992</v>
+        <v>122283857</v>
       </c>
       <c r="B9" t="n">
-        <v>97195</v>
+        <v>97190</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,38 +1536,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321665</v>
+        <v>321728</v>
       </c>
       <c r="R9" t="n">
-        <v>6430914</v>
+        <v>6430954</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1642,6 +1642,238 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124952862</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>321823</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6430793</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jörlanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillning spritt under betestall.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124952896</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8436</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>321870</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6430810</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jörlanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera rader med kläckhål i död björk.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -1644,10 +1644,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124952862</v>
+        <v>124952896</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>8436</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1660,29 +1660,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1692,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>321823</v>
+        <v>321870</v>
       </c>
       <c r="R10" t="n">
-        <v>6430793</v>
+        <v>6430810</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1732,7 +1733,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Spillning spritt under betestall.</t>
+          <t>Flera rader med kläckhål i död björk.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,6 +1742,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1759,10 +1761,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124952896</v>
+        <v>124952862</v>
       </c>
       <c r="B11" t="n">
-        <v>8436</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,30 +1777,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1808,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>321870</v>
+        <v>321823</v>
       </c>
       <c r="R11" t="n">
-        <v>6430810</v>
+        <v>6430793</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1848,7 +1849,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera rader med kläckhål i död björk.</t>
+          <t>Spillning spritt under betestall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,7 +1858,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -1644,10 +1644,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124952896</v>
+        <v>124952862</v>
       </c>
       <c r="B10" t="n">
-        <v>8436</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1660,30 +1660,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1693,10 +1692,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>321870</v>
+        <v>321823</v>
       </c>
       <c r="R10" t="n">
-        <v>6430810</v>
+        <v>6430793</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1733,7 +1732,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera rader med kläckhål i död björk.</t>
+          <t>Spillning spritt under betestall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,7 +1741,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1761,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124952862</v>
+        <v>124952896</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>8436</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1777,29 +1775,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1809,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>321823</v>
+        <v>321870</v>
       </c>
       <c r="R11" t="n">
-        <v>6430793</v>
+        <v>6430810</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1849,7 +1848,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spillning spritt under betestall.</t>
+          <t>Flera rader med kläckhål i död björk.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,6 +1857,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -1644,10 +1644,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124952862</v>
+        <v>124952896</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>8436</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1660,29 +1660,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1692,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>321823</v>
+        <v>321870</v>
       </c>
       <c r="R10" t="n">
-        <v>6430793</v>
+        <v>6430810</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1732,7 +1733,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Spillning spritt under betestall.</t>
+          <t>Flera rader med kläckhål i död björk.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,6 +1742,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1759,14 +1761,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124952896</v>
+        <v>124952862</v>
       </c>
       <c r="B11" t="n">
-        <v>8436</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1775,30 +1777,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1808,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>321870</v>
+        <v>321823</v>
       </c>
       <c r="R11" t="n">
-        <v>6430810</v>
+        <v>6430793</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1848,7 +1849,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera rader med kläckhål i död björk.</t>
+          <t>Spillning spritt under betestall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,7 +1858,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -1764,7 +1764,7 @@
         <v>124952862</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -1649,11 +1649,6 @@
       <c r="B10" t="n">
         <v>8436</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1764,12 +1759,7 @@
         <v>124952862</v>
       </c>
       <c r="B11" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122246733</v>
+        <v>122246765</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321530</v>
+        <v>321732</v>
       </c>
       <c r="R2" t="n">
-        <v>6430805</v>
+        <v>6430948</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,24 +751,14 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I talldominerad, skiktad skog nära mossen.</t>
+          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122246765</v>
+        <v>122246705</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,23 +818,23 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, väster om, Boh</t>
+          <t>Dyfjällernas mosse, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321732</v>
+        <v>321810</v>
       </c>
       <c r="R3" t="n">
-        <v>6430948</v>
+        <v>6430695</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +868,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack i stående död tall. Hård ved. Både äldre och nyare spår.</t>
+          <t>Några färska spillningar spridd på hällmarkparti. Även några äldre.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122246664</v>
+        <v>122246780</v>
       </c>
       <c r="B4" t="n">
-        <v>57753</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,49 +906,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 1291-2025, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321869</v>
+        <v>321791</v>
       </c>
       <c r="R4" t="n">
-        <v>6430770</v>
+        <v>6430952</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,24 +971,14 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 2 ex.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122283992</v>
+        <v>124952862</v>
       </c>
       <c r="B5" t="n">
-        <v>97198</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,41 +1016,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321665</v>
+        <v>321823</v>
       </c>
       <c r="R5" t="n">
-        <v>6430914</v>
+        <v>6430793</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,17 +1078,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer</t>
+          <t>Spillning spritt under betestall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,34 +1097,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stig Ingvarsson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stig Ingvarsson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122283846</v>
+        <v>122246664</v>
       </c>
       <c r="B6" t="n">
-        <v>97190</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224361</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1198,31 +1148,27 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
+          <t>A 1291-2025, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321686</v>
+        <v>321869</v>
       </c>
       <c r="R6" t="n">
-        <v>6430924</v>
+        <v>6430770</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,17 +1192,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,85 +1221,75 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stig Ingvarsson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stig Ingvarsson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122284108</v>
+        <v>122246733</v>
       </c>
       <c r="B7" t="n">
-        <v>97190</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224361</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+          <t>Dyfjällernas mosse, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321607</v>
+        <v>321530</v>
       </c>
       <c r="R7" t="n">
-        <v>6430823</v>
+        <v>6430805</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,17 +1316,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Nordvänd hällmark.</t>
+          <t>I talldominerad, skiktad skog nära mossen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,34 +1345,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stig Ingvarsson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stig Ingvarsson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122284062</v>
+        <v>124952896</v>
       </c>
       <c r="B8" t="n">
-        <v>97198</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,41 +1374,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
+          <t>Dyfjällernas mosse, väster om, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321729</v>
+        <v>321870</v>
       </c>
       <c r="R8" t="n">
-        <v>6430964</v>
+        <v>6430810</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1482,17 +1437,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Följeväxt äkta lopplummer.</t>
+          <t>Flera rader med kläckhål i död björk.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,27 +1463,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stig Ingvarsson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stig Ingvarsson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122283857</v>
+        <v>122283992</v>
       </c>
       <c r="B9" t="n">
-        <v>97190</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,50 +1486,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321728</v>
+        <v>321665</v>
       </c>
       <c r="R9" t="n">
-        <v>6430954</v>
+        <v>6430914</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,7 +1554,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+          <t>Följeväxt äkta lopplummer</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124952896</v>
+        <v>122284062</v>
       </c>
       <c r="B10" t="n">
-        <v>8436</v>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,46 +1593,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, väster om, Boh</t>
+          <t>Svartedalen,  700 m N St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>321870</v>
+        <v>321729</v>
       </c>
       <c r="R10" t="n">
-        <v>6430810</v>
+        <v>6430964</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1718,17 +1651,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera rader med kläckhål i död björk.</t>
+          <t>Följeväxt äkta lopplummer.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1744,22 +1677,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Stig Ingvarsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Stig Ingvarsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124952862</v>
+        <v>122283846</v>
       </c>
       <c r="B11" t="n">
-        <v>56843</v>
+        <v>97975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,45 +1700,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>224361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dyfjällernas mosse, väster om, Boh</t>
+          <t>Svartedalen, 650 m NNV St. Sutaren, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>321823</v>
+        <v>321686</v>
       </c>
       <c r="R11" t="n">
-        <v>6430793</v>
+        <v>6430924</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1829,17 +1770,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spillning spritt under betestall.</t>
+          <t>Nordvänd hällmark. Följeväxt revlummer.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,21 +1789,260 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Stig Ingvarsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Stig Ingvarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122283857</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svartedalen, 700 m N St. Sutaren, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>321728</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6430954</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jörlanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Nordvänd blockterräng, Följeväxt revlummer.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stig Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Stig Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122284108</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svartedalen, 600 m NNV St. Sutaren, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>321607</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6430823</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jörlanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Nordvänd hällmark.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Stig Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Stig Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1291-2025 artfynd.xlsx
+++ b/artfynd/A 1291-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122246765</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122246705</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122246780</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124952862</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122246664</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122246733</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1472,6 +1507,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124952896</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1579,6 +1619,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122283992</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1686,6 +1731,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122284062</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1805,6 +1855,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122283846</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1924,6 +1979,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122283857</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2043,8 +2103,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122284108</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>